--- a/data/homes6.xlsx
+++ b/data/homes6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ATS\crm_bunyodkorhouse\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA068615-10FE-40D5-88CE-57134F2919BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4383FF2-C231-415C-9139-683498EA364B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{E2C49507-81BE-4FB1-B64F-19DDB760E2A2}"/>
   </bookViews>
@@ -533,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A055130-5502-4B5D-8778-639AC477D802}">
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="36.21875" customWidth="1"/>
@@ -1477,6 +1477,108 @@
         <v>7000000</v>
       </c>
     </row>
+    <row r="56" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>-1</v>
+      </c>
+      <c r="B56" s="3">
+        <v>55</v>
+      </c>
+      <c r="C56" s="3">
+        <v>35.6</v>
+      </c>
+      <c r="D56" s="3">
+        <v>1</v>
+      </c>
+      <c r="E56" s="3">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="B57" s="5">
+        <v>56</v>
+      </c>
+      <c r="C57" s="5">
+        <v>73.2</v>
+      </c>
+      <c r="D57" s="5">
+        <v>3</v>
+      </c>
+      <c r="E57" s="5">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="B58" s="5">
+        <v>57</v>
+      </c>
+      <c r="C58" s="5">
+        <v>34</v>
+      </c>
+      <c r="D58" s="5">
+        <v>1</v>
+      </c>
+      <c r="E58" s="5">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="B59" s="5">
+        <v>58</v>
+      </c>
+      <c r="C59" s="5">
+        <v>34</v>
+      </c>
+      <c r="D59" s="5">
+        <v>1</v>
+      </c>
+      <c r="E59" s="5">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="B60" s="5">
+        <v>59</v>
+      </c>
+      <c r="C60" s="5">
+        <v>60</v>
+      </c>
+      <c r="D60" s="5">
+        <v>2</v>
+      </c>
+      <c r="E60" s="5">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="6">
+        <v>-1</v>
+      </c>
+      <c r="B61" s="7">
+        <v>60</v>
+      </c>
+      <c r="C61" s="7">
+        <v>49.3</v>
+      </c>
+      <c r="D61" s="7">
+        <v>2</v>
+      </c>
+      <c r="E61" s="7">
+        <v>7000000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
